--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.78463597103621</v>
+        <v>4.190003345293384</v>
       </c>
       <c r="D2" t="n">
-        <v>21.28439837484018</v>
+        <v>3.458714735911529</v>
       </c>
       <c r="E2" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F2" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.163407649184469</v>
+        <v>1.489053742992476</v>
       </c>
       <c r="D3" t="n">
-        <v>11.89757534040629</v>
+        <v>1.933355992816022</v>
       </c>
       <c r="E3" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F3" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.70573806522604</v>
+        <v>3.202182435599231</v>
       </c>
       <c r="D4" t="n">
-        <v>11.72393129726539</v>
+        <v>1.905138835805626</v>
       </c>
       <c r="E4" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F4" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.98136983405529</v>
+        <v>10.39697259803398</v>
       </c>
       <c r="D5" t="n">
-        <v>34.20478220402561</v>
+        <v>5.558277108154161</v>
       </c>
       <c r="E5" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F5" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.44589275001664</v>
+        <v>2.022457571877704</v>
       </c>
       <c r="D6" t="n">
-        <v>9.168012410216766</v>
+        <v>1.489802016660225</v>
       </c>
       <c r="E6" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F6" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.37908986756938</v>
+        <v>5.424102103480024</v>
       </c>
       <c r="D7" t="n">
-        <v>3.298128839849647</v>
+        <v>0.5359459364755678</v>
       </c>
       <c r="E7" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F7" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.52699291723513</v>
+        <v>2.685636349050709</v>
       </c>
       <c r="D8" t="n">
-        <v>13.9516573966332</v>
+        <v>2.267144326952895</v>
       </c>
       <c r="E8" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F8" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>78.94341752184826</v>
+        <v>12.82830534730034</v>
       </c>
       <c r="D9" t="n">
-        <v>46.76069255802066</v>
+        <v>7.598612540678357</v>
       </c>
       <c r="E9" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F9" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.055764533740982</v>
+        <v>0.4965617367329095</v>
       </c>
       <c r="D10" t="n">
-        <v>8.919855646492607</v>
+        <v>1.449476542555049</v>
       </c>
       <c r="E10" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F10" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>82.68490072703223</v>
+        <v>13.43629636814274</v>
       </c>
       <c r="D11" t="n">
-        <v>40.0780488547035</v>
+        <v>6.512682938889318</v>
       </c>
       <c r="E11" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F11" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>101.3521536024413</v>
+        <v>16.46972496039671</v>
       </c>
       <c r="D12" t="n">
-        <v>51.61595942490924</v>
+        <v>8.387593406547753</v>
       </c>
       <c r="E12" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F12" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>80.78037825281339</v>
+        <v>13.12681146608218</v>
       </c>
       <c r="D13" t="n">
-        <v>35.42950747611375</v>
+        <v>5.757294964868485</v>
       </c>
       <c r="E13" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F13" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>73.17159138458264</v>
+        <v>11.89038359999468</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03626910567699</v>
+        <v>5.043393729672511</v>
       </c>
       <c r="E14" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F14" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>82.80927340837455</v>
+        <v>13.45650692886086</v>
       </c>
       <c r="D15" t="n">
-        <v>34.00367627183861</v>
+        <v>5.525597394173774</v>
       </c>
       <c r="E15" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F15" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.45958910654407</v>
+        <v>5.924683229813411</v>
       </c>
       <c r="D16" t="n">
-        <v>14.84598413966845</v>
+        <v>2.412472422696123</v>
       </c>
       <c r="E16" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F16" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.66900786920241</v>
+        <v>2.546213778745392</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8379323458973</v>
+        <v>1.923664006208312</v>
       </c>
       <c r="E17" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F17" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.7556901952105</v>
+        <v>8.735299656721706</v>
       </c>
       <c r="D18" t="n">
-        <v>28.43720002867202</v>
+        <v>4.621045004659202</v>
       </c>
       <c r="E18" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F18" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>94.09701315034792</v>
+        <v>15.29076463693154</v>
       </c>
       <c r="D19" t="n">
-        <v>40.39895493740789</v>
+        <v>6.564830177328782</v>
       </c>
       <c r="E19" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F19" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24.21908864382085</v>
+        <v>3.935601904620888</v>
       </c>
       <c r="D20" t="n">
-        <v>18.95804319687929</v>
+        <v>3.080682019492885</v>
       </c>
       <c r="E20" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F20" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>80.11255121301234</v>
+        <v>13.01828957211451</v>
       </c>
       <c r="D21" t="n">
-        <v>26.4211588058649</v>
+        <v>4.293438305953046</v>
       </c>
       <c r="E21" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F21" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>86.15874547896688</v>
+        <v>14.00079614033212</v>
       </c>
       <c r="D22" t="n">
-        <v>29.4500129543303</v>
+        <v>4.785627105078675</v>
       </c>
       <c r="E22" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F22" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>42.08905605485047</v>
+        <v>6.839471608913202</v>
       </c>
       <c r="D23" t="n">
-        <v>36.55979463957013</v>
+        <v>5.940966628930146</v>
       </c>
       <c r="E23" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F23" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>31.3883056492264</v>
+        <v>5.10059966799929</v>
       </c>
       <c r="D24" t="n">
-        <v>32.04601947969618</v>
+        <v>5.207478165450629</v>
       </c>
       <c r="E24" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F24" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>40.19842707881855</v>
+        <v>6.532244400308016</v>
       </c>
       <c r="D25" t="n">
-        <v>39.49505062806118</v>
+        <v>6.417945727059942</v>
       </c>
       <c r="E25" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F25" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>76.91807629107923</v>
+        <v>12.49918739730037</v>
       </c>
       <c r="D26" t="n">
-        <v>20.23074874440848</v>
+        <v>3.287496670966378</v>
       </c>
       <c r="E26" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F26" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>58.90796184128187</v>
+        <v>9.572543799208304</v>
       </c>
       <c r="D27" t="n">
-        <v>15.14594054682459</v>
+        <v>2.461215338858995</v>
       </c>
       <c r="E27" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F27" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>14.8154426537419</v>
+        <v>2.407509431233058</v>
       </c>
       <c r="D28" t="n">
-        <v>15.58908643153883</v>
+        <v>2.53322654512506</v>
       </c>
       <c r="E28" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F28" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>33.4474352714568</v>
+        <v>5.435208231611731</v>
       </c>
       <c r="D29" t="n">
-        <v>21.24833488857869</v>
+        <v>3.452854419394037</v>
       </c>
       <c r="E29" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F29" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>20.42780659095449</v>
+        <v>3.319518571030105</v>
       </c>
       <c r="D30" t="n">
-        <v>20.99461651182696</v>
+        <v>3.411625183171882</v>
       </c>
       <c r="E30" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F30" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>52.65005239052129</v>
+        <v>8.555633513459711</v>
       </c>
       <c r="D31" t="n">
-        <v>10.82955338439295</v>
+        <v>1.759802424963855</v>
       </c>
       <c r="E31" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F31" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>37.12200864572484</v>
+        <v>6.032326404930287</v>
       </c>
       <c r="D32" t="n">
-        <v>37.75665619581345</v>
+        <v>6.135456631819686</v>
       </c>
       <c r="E32" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F32" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>47.57016910715041</v>
+        <v>7.730152479911943</v>
       </c>
       <c r="D33" t="n">
-        <v>13.32070235051857</v>
+        <v>2.164614131959268</v>
       </c>
       <c r="E33" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F33" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>34.34670356120484</v>
+        <v>5.581339328695787</v>
       </c>
       <c r="D34" t="n">
-        <v>24.70323865407125</v>
+        <v>4.014276281286578</v>
       </c>
       <c r="E34" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F34" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>57.12046380399179</v>
+        <v>9.282075368148666</v>
       </c>
       <c r="D35" t="n">
-        <v>5.689854518741629</v>
+        <v>0.9246013592955147</v>
       </c>
       <c r="E35" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F35" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>35.42657148774266</v>
+        <v>5.756817866758182</v>
       </c>
       <c r="D36" t="n">
-        <v>21.81216034596959</v>
+        <v>3.544476056220058</v>
       </c>
       <c r="E36" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F36" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>30.98423511484463</v>
+        <v>5.034938206162252</v>
       </c>
       <c r="D37" t="n">
-        <v>29.70269348055829</v>
+        <v>4.826687690590723</v>
       </c>
       <c r="E37" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F37" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>14.47720880217442</v>
+        <v>2.352546430353343</v>
       </c>
       <c r="D38" t="n">
-        <v>14.44566871085148</v>
+        <v>2.347421165513365</v>
       </c>
       <c r="E38" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F38" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>77.88605447482649</v>
+        <v>12.65648385215931</v>
       </c>
       <c r="D39" t="n">
-        <v>33.05861687647927</v>
+        <v>5.372025242427882</v>
       </c>
       <c r="E39" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F39" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>5.913868447875832</v>
+        <v>0.9610036227798228</v>
       </c>
       <c r="D40" t="n">
-        <v>6.105012223115732</v>
+        <v>0.9920644862563064</v>
       </c>
       <c r="E40" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F40" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>23.79419975064764</v>
+        <v>3.866557459480242</v>
       </c>
       <c r="D41" t="n">
-        <v>23.65761341592579</v>
+        <v>3.844362180087941</v>
       </c>
       <c r="E41" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F41" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>51.91659035938721</v>
+        <v>8.436445933400421</v>
       </c>
       <c r="D42" t="n">
-        <v>4.782484584988716</v>
+        <v>0.7771537450606665</v>
       </c>
       <c r="E42" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F42" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>60.3238343356735</v>
+        <v>9.802623079546944</v>
       </c>
       <c r="D43" t="n">
-        <v>5.076853793881058</v>
+        <v>0.8249887415056719</v>
       </c>
       <c r="E43" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F43" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>55.14726227283032</v>
+        <v>8.961430119334928</v>
       </c>
       <c r="D44" t="n">
-        <v>19.58306038813055</v>
+        <v>3.182247313071214</v>
       </c>
       <c r="E44" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F44" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>16.97967903649774</v>
+        <v>2.759197843430883</v>
       </c>
       <c r="D45" t="n">
-        <v>16.71135901367623</v>
+        <v>2.715595839722387</v>
       </c>
       <c r="E45" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F45" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>4.182212271442801</v>
+        <v>0.6796094941094553</v>
       </c>
       <c r="D46" t="n">
-        <v>3.406124154636629</v>
+        <v>0.5534951751284523</v>
       </c>
       <c r="E46" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F46" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>9.733014121001283</v>
+        <v>1.581614794662708</v>
       </c>
       <c r="D47" t="n">
-        <v>8.994930390249452</v>
+        <v>1.461676188415536</v>
       </c>
       <c r="E47" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F47" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>19.6256948249598</v>
+        <v>3.189175409055968</v>
       </c>
       <c r="D48" t="n">
-        <v>19.1708419689474</v>
+        <v>3.115261819953953</v>
       </c>
       <c r="E48" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F48" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>62.91381578400487</v>
+        <v>10.22349506490079</v>
       </c>
       <c r="D49" t="n">
-        <v>33.60858763788436</v>
+        <v>5.461395491156208</v>
       </c>
       <c r="E49" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F49" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>29.674290967851</v>
+        <v>4.822072282275788</v>
       </c>
       <c r="D50" t="n">
-        <v>29.28154199038607</v>
+        <v>4.758250573437736</v>
       </c>
       <c r="E50" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F50" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>17.09368728778301</v>
+        <v>2.777724184264739</v>
       </c>
       <c r="D51" t="n">
-        <v>16.41991047582806</v>
+        <v>2.66823545232206</v>
       </c>
       <c r="E51" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F51" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>15.76337117594733</v>
+        <v>2.561547816091442</v>
       </c>
       <c r="D52" t="n">
-        <v>14.98555155516411</v>
+        <v>2.435152127714167</v>
       </c>
       <c r="E52" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F52" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>41.01734360499519</v>
+        <v>6.665318335811719</v>
       </c>
       <c r="D53" t="n">
-        <v>38.54784466452308</v>
+        <v>6.264024757985</v>
       </c>
       <c r="E53" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F53" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>74.71636415150229</v>
+        <v>12.14140917461912</v>
       </c>
       <c r="D54" t="n">
-        <v>39.20518467944108</v>
+        <v>6.370842510409176</v>
       </c>
       <c r="E54" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F54" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>24.50202485056743</v>
+        <v>3.981579038217208</v>
       </c>
       <c r="D55" t="n">
-        <v>23.84716747406391</v>
+        <v>3.875164714535385</v>
       </c>
       <c r="E55" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F55" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>34.49527722885723</v>
+        <v>5.605482549689301</v>
       </c>
       <c r="D56" t="n">
-        <v>34.07642401335954</v>
+        <v>5.537418902170926</v>
       </c>
       <c r="E56" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F56" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>72.50881406790423</v>
+        <v>11.78268228603444</v>
       </c>
       <c r="D57" t="n">
-        <v>24.49227131917584</v>
+        <v>3.979994089366075</v>
       </c>
       <c r="E57" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F57" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>66.50266455063988</v>
+        <v>10.80668298947898</v>
       </c>
       <c r="D58" t="n">
-        <v>44.48299578622094</v>
+        <v>7.228486815260903</v>
       </c>
       <c r="E58" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F58" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>27.35391683050786</v>
+        <v>4.445011484957528</v>
       </c>
       <c r="D59" t="n">
-        <v>26.58752680866034</v>
+        <v>4.320473106407305</v>
       </c>
       <c r="E59" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F59" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>76.06313916644973</v>
+        <v>12.36026011454808</v>
       </c>
       <c r="D60" t="n">
-        <v>52.53200389334663</v>
+        <v>8.536450632668828</v>
       </c>
       <c r="E60" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F60" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>34.87075572837721</v>
+        <v>5.666497805861297</v>
       </c>
       <c r="D61" t="n">
-        <v>34.17437989274406</v>
+        <v>5.55333673257091</v>
       </c>
       <c r="E61" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F61" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>71.22735260701562</v>
+        <v>11.57444479864004</v>
       </c>
       <c r="D62" t="n">
-        <v>55.90109409326143</v>
+        <v>9.083927790154984</v>
       </c>
       <c r="E62" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F62" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>86.55244560092494</v>
+        <v>14.0647724101503</v>
       </c>
       <c r="D63" t="n">
-        <v>63.52516994013794</v>
+        <v>10.32284011527242</v>
       </c>
       <c r="E63" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F63" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>76.13339939021601</v>
+        <v>12.3716774009101</v>
       </c>
       <c r="D64" t="n">
-        <v>36.69933393279926</v>
+        <v>5.963641764079879</v>
       </c>
       <c r="E64" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F64" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>63.21105503480449</v>
+        <v>10.27179644315573</v>
       </c>
       <c r="D65" t="n">
-        <v>38.05401132308889</v>
+        <v>6.183776840001944</v>
       </c>
       <c r="E65" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F65" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>48.429612713888</v>
+        <v>7.8698120660068</v>
       </c>
       <c r="D66" t="n">
-        <v>47.74556190207996</v>
+        <v>7.758653809087993</v>
       </c>
       <c r="E66" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F66" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>48.31394084578628</v>
+        <v>7.851015387440271</v>
       </c>
       <c r="D67" t="n">
-        <v>47.71872480870026</v>
+        <v>7.754292781413792</v>
       </c>
       <c r="E67" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F67" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>73.96852504163328</v>
+        <v>12.01988531926541</v>
       </c>
       <c r="D68" t="n">
-        <v>63.9961359535215</v>
+        <v>10.39937209244724</v>
       </c>
       <c r="E68" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F68" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>63.60125858741036</v>
+        <v>10.33520452045418</v>
       </c>
       <c r="D69" t="n">
-        <v>63.0187986041842</v>
+        <v>10.24055477317993</v>
       </c>
       <c r="E69" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F69" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>80.41446896888627</v>
+        <v>13.06735120744402</v>
       </c>
       <c r="D70" t="n">
-        <v>65.16537826777295</v>
+        <v>10.5893739685131</v>
       </c>
       <c r="E70" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F70" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>58.24135865923935</v>
+        <v>9.464220782126395</v>
       </c>
       <c r="D71" t="n">
-        <v>57.62776135502403</v>
+        <v>9.364511220191407</v>
       </c>
       <c r="E71" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F71" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>58.71063597123783</v>
+        <v>9.540478345326147</v>
       </c>
       <c r="D72" t="n">
-        <v>58.03158924988738</v>
+        <v>9.430133253106698</v>
       </c>
       <c r="E72" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F72" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>81.64542049434061</v>
+        <v>13.26738083033035</v>
       </c>
       <c r="D73" t="n">
-        <v>49.83279821340336</v>
+        <v>8.097829709678047</v>
       </c>
       <c r="E73" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F73" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>83.9619296748776</v>
+        <v>13.64381357216761</v>
       </c>
       <c r="D74" t="n">
-        <v>76.77090132333657</v>
+        <v>12.47527146504219</v>
       </c>
       <c r="E74" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F74" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>52.58289988041356</v>
+        <v>8.544721230567204</v>
       </c>
       <c r="D75" t="n">
-        <v>51.82454654991595</v>
+        <v>8.421488814361343</v>
       </c>
       <c r="E75" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F75" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>74.02241080326017</v>
+        <v>12.02864175552978</v>
       </c>
       <c r="D76" t="n">
-        <v>73.38727320215204</v>
+        <v>11.92543189534971</v>
       </c>
       <c r="E76" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F76" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>67.29196283470735</v>
+        <v>10.93494396063995</v>
       </c>
       <c r="D77" t="n">
-        <v>66.56368865375646</v>
+        <v>10.81659940623542</v>
       </c>
       <c r="E77" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F77" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>96.98120961950086</v>
+        <v>15.75944656316889</v>
       </c>
       <c r="D78" t="n">
-        <v>84.82122907974717</v>
+        <v>13.78344972545892</v>
       </c>
       <c r="E78" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F78" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>87.6777236992039</v>
+        <v>14.24763010112063</v>
       </c>
       <c r="D79" t="n">
-        <v>86.74463903382497</v>
+        <v>14.09600384299656</v>
       </c>
       <c r="E79" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F79" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>80.40551694199434</v>
+        <v>13.06589650307408</v>
       </c>
       <c r="D80" t="n">
-        <v>79.72877056373643</v>
+        <v>12.95592521660717</v>
       </c>
       <c r="E80" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F80" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>79.5812561212898</v>
+        <v>12.93195411970959</v>
       </c>
       <c r="D81" t="n">
-        <v>78.86234281225072</v>
+        <v>12.81513070699074</v>
       </c>
       <c r="E81" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F81" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>93.464477889047</v>
+        <v>15.18797765697014</v>
       </c>
       <c r="D82" t="n">
-        <v>91.92895566649047</v>
+        <v>14.9384552958047</v>
       </c>
       <c r="E82" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F82" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>96.12079718522479</v>
+        <v>15.61962954259903</v>
       </c>
       <c r="D83" t="n">
-        <v>89.03644257000543</v>
+        <v>14.46842191762588</v>
       </c>
       <c r="E83" t="n">
-        <v>27.12703590156358</v>
+        <v>4.408143334004081</v>
       </c>
       <c r="F83" t="n">
-        <v>22.59562026904809</v>
+        <v>3.671788293720314</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
